--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484775_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484775_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3963</v>
+        <v>4.2934</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.1618</v>
+        <v>-0.2648</v>
       </c>
       <c r="F2" t="n">
         <v>4.5582</v>
@@ -610,10 +610,10 @@
         <v>3.0192</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0023</v>
+        <v>-0.1052</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.0452</v>
+        <v>-1.1482</v>
       </c>
       <c r="U2" t="n">
         <v>1.0429</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7004</v>
+        <v>2.139</v>
       </c>
       <c r="E3" t="n">
-        <v>1.184</v>
+        <v>-2.4159</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5164</v>
+        <v>4.5548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2664</v>
+        <v>1.2666</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1213</v>
+        <v>0.2559</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3877</v>
+        <v>1.0107</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5224</v>
+        <v>0.2666</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1308</v>
+        <v>0.3388</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.0723</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.256</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2521</v>
+        <v>-0.0829</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9962</v>
+        <v>1.083</v>
       </c>
       <c r="P3" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6983</v>
+        <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0945</v>
+        <v>0.1176</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0204</v>
+        <v>-0.7955</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0741</v>
+        <v>0.913</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5846</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5846</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3007</v>
+        <v>1.8726</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.2542</v>
+        <v>0.171</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5548</v>
+        <v>1.7016</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2666</v>
+        <v>0.2664</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2559</v>
+        <v>-0.1213</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0107</v>
+        <v>0.3877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2666</v>
+        <v>0.5224</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3388</v>
+        <v>1.1308</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0723</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>-0.256</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0829</v>
+        <v>-1.2521</v>
       </c>
       <c r="O4" t="n">
-        <v>1.083</v>
+        <v>0.9962</v>
       </c>
       <c r="P4" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6418</v>
+        <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7207</v>
+        <v>0.2667</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6337</v>
+        <v>0.0074</v>
       </c>
       <c r="U4" t="n">
-        <v>0.913</v>
+        <v>0.2593</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5846</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5846</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.139</v>
+        <v>1.3888</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3329</v>
+        <v>-1.2153</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4719</v>
+        <v>2.6041</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4243</v>
@@ -844,13 +844,13 @@
         <v>3.2079</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.6873</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7073</v>
+        <v>0.8395</v>
       </c>
       <c r="V5" t="n">
         <v>-1.547</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3425</v>
+        <v>-0.3302</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3516</v>
+        <v>-0.3491</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0091</v>
+        <v>0.019</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4559</v>
+        <v>-0.913</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4127</v>
+        <v>-0.5017</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0431</v>
+        <v>-0.4113</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1935</v>
+        <v>-0.2904</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1935</v>
+        <v>-0.2904</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2624</v>
+        <v>-0.6226</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2193</v>
+        <v>-0.2113</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0431</v>
+        <v>-0.4113</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7418</v>
+        <v>-0.0588</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2432</v>
+        <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4985</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3018</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.233</v>
+        <v>-0.4192</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0606</v>
+        <v>-3.5276</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2936</v>
+        <v>3.1084</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2049</v>
@@ -1000,13 +1000,13 @@
         <v>2.6418</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3056</v>
+        <v>0.6534</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0798</v>
+        <v>-0.3872</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2258</v>
+        <v>1.0406</v>
       </c>
       <c r="V7" t="n">
         <v>-1.566</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3302</v>
+        <v>-0.5144</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3491</v>
+        <v>-1.504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.019</v>
+        <v>0.9896</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.913</v>
+        <v>2.911</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5017</v>
+        <v>2.3071</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4113</v>
+        <v>0.6039</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2904</v>
+        <v>2.0889</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2904</v>
+        <v>2.113</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.0241</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6226</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2113</v>
+        <v>0.1941</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4113</v>
+        <v>0.628</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0588</v>
+        <v>0.3859</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0588</v>
+        <v>-0.1208</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.5068</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6415999999999999</v>
+        <v>-2.4904</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2371</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1474</v>
+        <v>-0.4665</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9103</v>
+        <v>-0.1943</v>
       </c>
       <c r="G9" t="n">
-        <v>2.911</v>
+        <v>-2.4559</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3071</v>
+        <v>-2.4127</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6039</v>
+        <v>-0.0431</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0889</v>
+        <v>-1.1935</v>
       </c>
       <c r="K9" t="n">
-        <v>2.113</v>
+        <v>-1.1935</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0241</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8221000000000001</v>
+        <v>-1.2624</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1941</v>
+        <v>-1.2193</v>
       </c>
       <c r="O9" t="n">
-        <v>0.628</v>
+        <v>-0.0431</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3368</v>
+        <v>0.7385</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7642</v>
+        <v>0.4251</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4274</v>
+        <v>0.3134</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4904</v>
+        <v>0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4301</v>
+        <v>-2.3411</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3823</v>
+        <v>-0.1874</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0478</v>
+        <v>-2.1536</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4817</v>
@@ -1234,13 +1234,13 @@
         <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0241</v>
+        <v>0.065</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5291</v>
+        <v>-0.3342</v>
       </c>
       <c r="U10" t="n">
-        <v>0.505</v>
+        <v>0.3992</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4904</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.74</v>
+        <v>-2.4658</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1737</v>
+        <v>-0.9788</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5664</v>
+        <v>-1.487</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6732</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1235</v>
+        <v>0.1508</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0529</v>
+        <v>0.1323</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9434</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.374499999999999</v>
+        <v>2.962299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.3264</v>
+        <v>-10.7384</v>
       </c>
       <c r="F12" t="n">
-        <v>13.7009</v>
+        <v>13.7008</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9141</v>
@@ -1366,7 +1366,7 @@
         <v>-1.5237</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1013999999999995</v>
+        <v>0.1014000000000002</v>
       </c>
       <c r="L12" t="n">
         <v>-1.6253</v>
@@ -1390,13 +1390,13 @@
         <v>16.0395</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7781</v>
+        <v>2.3661</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6689</v>
+        <v>-3.081</v>
       </c>
       <c r="U12" t="n">
-        <v>5.4469</v>
+        <v>5.447</v>
       </c>
       <c r="V12" t="n">
         <v>-5.981200000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9912</v>
+        <v>4.448</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2242</v>
+        <v>0.7627</v>
       </c>
       <c r="F13" t="n">
-        <v>3.767</v>
+        <v>3.6853</v>
       </c>
       <c r="G13" t="n">
         <v>3.2785</v>
@@ -1468,13 +1468,13 @@
         <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0522</v>
+        <v>0.5089</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5401</v>
+        <v>0.0786</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5121</v>
+        <v>0.4304</v>
       </c>
       <c r="V13" t="n">
         <v>0.6606</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3104</v>
+        <v>2.4764</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0062</v>
+        <v>0.1887</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3165</v>
+        <v>2.2877</v>
       </c>
       <c r="G14" t="n">
         <v>6.1758</v>
@@ -1546,13 +1546,13 @@
         <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3932</v>
+        <v>-0.2272</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9406</v>
+        <v>-0.7457</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5474</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.3018</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2374</v>
+        <v>1.1183</v>
       </c>
       <c r="E15" t="n">
-        <v>0.036</v>
+        <v>-0.4512</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2015</v>
+        <v>1.5695</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3288</v>
@@ -1624,13 +1624,13 @@
         <v>0.9435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0194</v>
+        <v>-0.0998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1706</v>
+        <v>-0.6577</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1899</v>
+        <v>0.5579</v>
       </c>
       <c r="V15" t="n">
         <v>2.4904</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5803</v>
+        <v>0.732</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.99</v>
+        <v>-0.6002</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5703</v>
+        <v>1.3322</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6253</v>
@@ -1702,13 +1702,13 @@
         <v>0.5661</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1152</v>
+        <v>0.0365</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2933</v>
+        <v>-0.9036</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1782</v>
+        <v>0.9401</v>
       </c>
       <c r="V16" t="n">
         <v>0.9434</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1581</v>
+        <v>0.1028</v>
       </c>
       <c r="E17" t="n">
         <v>-0.4363</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5944</v>
+        <v>0.5391</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1472</v>
@@ -1780,13 +1780,13 @@
         <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0036</v>
+        <v>-0.0517</v>
       </c>
       <c r="T17" t="n">
         <v>-0.8789</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8825</v>
+        <v>0.8272</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0999</v>
+        <v>0.0239</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0999</v>
+        <v>0.0239</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1274</v>
+        <v>-0.0564</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2216</v>
+        <v>-0.1242</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0678</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3572</v>
@@ -1936,13 +1936,13 @@
         <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3362</v>
+        <v>-0.2653</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4328</v>
+        <v>-1.0263</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5645</v>
+        <v>-1.3696</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1317</v>
+        <v>0.3433</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0223</v>
@@ -2014,13 +2014,13 @@
         <v>0.7548</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.92</v>
+        <v>-0.5135</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4703</v>
+        <v>-0.2754</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4497</v>
+        <v>-0.238</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9483</v>
+        <v>-3.4263</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7401</v>
+        <v>-3.3504</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2082</v>
+        <v>-0.0759</v>
       </c>
       <c r="G21" t="n">
         <v>-3.514</v>
@@ -2092,13 +2092,13 @@
         <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6419</v>
+        <v>-0.1199</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.117</v>
+        <v>-0.7272</v>
       </c>
       <c r="U21" t="n">
-        <v>0.475</v>
+        <v>0.6073</v>
       </c>
       <c r="V21" t="n">
         <v>0.019</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.0435</v>
+        <v>-6.1173</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.8849</v>
+        <v>-8.3003</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8414</v>
+        <v>2.1829</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5454</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3467</v>
+        <v>-0.4206</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.6461</v>
+        <v>-1.0614</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2993</v>
+        <v>0.6409</v>
       </c>
       <c r="V22" t="n">
         <v>0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.374499999999999</v>
+        <v>-1.724899999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-13.701</v>
+        <v>-13.7009</v>
       </c>
       <c r="F23" t="n">
-        <v>11.3264</v>
+        <v>11.976</v>
       </c>
       <c r="G23" t="n">
         <v>1.9141</v>
@@ -2248,13 +2248,13 @@
         <v>7.548</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7779</v>
+        <v>-1.1287</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.447</v>
+        <v>-5.4467</v>
       </c>
       <c r="U23" t="n">
-        <v>3.6688</v>
+        <v>4.3185</v>
       </c>
       <c r="V23" t="n">
         <v>5.981200000000001</v>
